--- a/data_out/country_spreadsheets/Belgium.xlsx
+++ b/data_out/country_spreadsheets/Belgium.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W45"/>
+  <dimension ref="A1:AN45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,87 +461,172 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Median drought days per year</t>
+          <t>Median drought-warning-days</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Maximum recorded drought days per year</t>
+          <t>Maximum recorded drought-warning-days</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>most severe drought year</t>
+          <t>Year of maximum drought-warning-days</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2012</t>
+          <t>Warning days 2012</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2013</t>
+          <t>Warning days 2013</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2014</t>
+          <t>Warning days 2014</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2015</t>
+          <t>Warning days 2015</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2016</t>
+          <t>Warning days 2016</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2017</t>
+          <t>Warning days 2017</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2018</t>
+          <t>Warning days 2018</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2019</t>
+          <t>Warning days 2019</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2020</t>
+          <t>Warning days 2020</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2021</t>
+          <t>Warning days 2021</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2022</t>
+          <t>Warning days 2022</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2023</t>
+          <t>Warning days 2023</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2024</t>
+          <t>Warning days 2024</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>Drought days 2025</t>
+          <t>Warning days 2025</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Median drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Maximum recorded drought-alert-days</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Year of maximum drought-alert-days</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2012</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2013</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2014</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2015</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2016</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2017</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2018</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2019</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2020</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2021</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2022</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2023</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2024</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>Alert days 2025</t>
         </is>
       </c>
     </row>
@@ -621,6 +706,57 @@
       <c r="W2" t="n">
         <v>288.71</v>
       </c>
+      <c r="X2" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>6.97</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10.37</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>86.83</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>184.88</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>186.8</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>192.12</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>57.33</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>250.22</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>34.65</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>248.83</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>40.55</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>288.71</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -698,6 +834,57 @@
       <c r="W3" t="n">
         <v>257.29</v>
       </c>
+      <c r="X3" t="n">
+        <v>3.24</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>22.94</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>14.54</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>43</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>31.68</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>6.08</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>69.66</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>185.96</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>115.13</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>139.18</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>15.4</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>111.25</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>82.08</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>257.29</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -775,6 +962,57 @@
       <c r="W4" t="n">
         <v>258.9</v>
       </c>
+      <c r="X4" t="n">
+        <v>3.22</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>49.23</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>40.91</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>7.51</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>30.69</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>8.720000000000001</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>151.72</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>181.82</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>161.51</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>190.54</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>25.32</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>132.06</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>63.98</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>258.9</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -852,6 +1090,57 @@
       <c r="W5" t="n">
         <v>163.82</v>
       </c>
+      <c r="X5" t="n">
+        <v>6.33</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>31.22</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>60.52</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>31.84</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>185.34</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>83.25</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>90.98999999999999</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>41.72</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>163.82</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -929,6 +1218,57 @@
       <c r="W6" t="n">
         <v>246.49</v>
       </c>
+      <c r="X6" t="n">
+        <v>8.119999999999999</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>34.48</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>41.68</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>130.35</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>131.57</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>54.14</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>19.44</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>148.39</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>180.61</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>88.04000000000001</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>229.51</v>
+      </c>
+      <c r="AJ6" t="n">
+        <v>24.65</v>
+      </c>
+      <c r="AK6" t="n">
+        <v>195.55</v>
+      </c>
+      <c r="AL6" t="n">
+        <v>47.24</v>
+      </c>
+      <c r="AM6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>246.49</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1006,6 +1346,57 @@
       <c r="W7" t="n">
         <v>213.86</v>
       </c>
+      <c r="X7" t="n">
+        <v>5.74</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>31.16</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>24.79</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>72</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>51.94</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>23.63</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>174.65</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>139.12</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>215.51</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>37.83</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>97.56999999999999</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>10.59</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>213.86</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1083,6 +1474,57 @@
       <c r="W8" t="n">
         <v>149.98</v>
       </c>
+      <c r="X8" t="n">
+        <v>6.42</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>38.58</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2018</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>24.92</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>9.970000000000001</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>31.57</v>
+      </c>
+      <c r="AD8" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>85.76000000000001</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>177.19</v>
+      </c>
+      <c r="AH8" t="n">
+        <v>325.15</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>334.65</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>101.83</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>14.07</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>149.98</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1160,6 +1602,57 @@
       <c r="W9" t="n">
         <v>261.29</v>
       </c>
+      <c r="X9" t="n">
+        <v>8.82</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>62.12</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA9" t="n">
+        <v>26.66</v>
+      </c>
+      <c r="AB9" t="n">
+        <v>12.15</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>178</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>229.31</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>207.13</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>44.25</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>239.37</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>37.63</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>261.29</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1237,6 +1730,57 @@
       <c r="W10" t="n">
         <v>274.57</v>
       </c>
+      <c r="X10" t="n">
+        <v>5.11</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>66.45999999999999</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>28.5</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>17.95</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>34.93</v>
+      </c>
+      <c r="AE10" t="n">
+        <v>9.48</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>150.6</v>
+      </c>
+      <c r="AG10" t="n">
+        <v>186.29</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>188.36</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>197.92</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>32.55</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>168.52</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>67.23</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>274.57</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1314,6 +1858,57 @@
       <c r="W11" t="n">
         <v>273.9</v>
       </c>
+      <c r="X11" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>80.3</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>51.55</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>4.39</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>7.49</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>60.76</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>63.38</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>158.52</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>239.84</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>29.67</v>
+      </c>
+      <c r="AK11" t="n">
+        <v>149.12</v>
+      </c>
+      <c r="AL11" t="n">
+        <v>59.62</v>
+      </c>
+      <c r="AM11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>273.9</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1391,6 +1986,57 @@
       <c r="W12" t="n">
         <v>271.45</v>
       </c>
+      <c r="X12" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>65.31</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="AD12" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>24.97</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>160.09</v>
+      </c>
+      <c r="AG12" t="n">
+        <v>172.46</v>
+      </c>
+      <c r="AH12" t="n">
+        <v>245.8</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>230.03</v>
+      </c>
+      <c r="AJ12" t="n">
+        <v>45</v>
+      </c>
+      <c r="AK12" t="n">
+        <v>160.77</v>
+      </c>
+      <c r="AL12" t="n">
+        <v>60.81</v>
+      </c>
+      <c r="AM12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>271.45</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1468,6 +2114,57 @@
       <c r="W13" t="n">
         <v>253.51</v>
       </c>
+      <c r="X13" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>22.91</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>17.49</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>42.97</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>10.84</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>201.64</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>165.59</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>283.96</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>245.79</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>75.02</v>
+      </c>
+      <c r="AK13" t="n">
+        <v>217.57</v>
+      </c>
+      <c r="AL13" t="n">
+        <v>50.36</v>
+      </c>
+      <c r="AM13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>253.51</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1545,6 +2242,57 @@
       <c r="W14" t="n">
         <v>272.95</v>
       </c>
+      <c r="X14" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>63.24</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>9.279999999999999</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>22.92</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>58.18</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>19.43</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>108.86</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>189.64</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>132.22</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>168.36</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>28.87</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>126.17</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>70.27</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>272.95</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1622,6 +2370,57 @@
       <c r="W15" t="n">
         <v>269.54</v>
       </c>
+      <c r="X15" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>46.45</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>19.89</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>68</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>132.37</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>187.01</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>185.77</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>97.01000000000001</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>232.91</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>49.54</v>
+      </c>
+      <c r="AK15" t="n">
+        <v>236.6</v>
+      </c>
+      <c r="AL15" t="n">
+        <v>46.4</v>
+      </c>
+      <c r="AM15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>269.54</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1699,6 +2498,57 @@
       <c r="W16" t="n">
         <v>233.29</v>
       </c>
+      <c r="X16" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>57.06</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>19.28</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>15.37</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>53.28</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>54.45</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>7.85</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>148.53</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>203.39</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>194.57</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>214.95</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>31.31</v>
+      </c>
+      <c r="AK16" t="n">
+        <v>132.86</v>
+      </c>
+      <c r="AL16" t="n">
+        <v>18.19</v>
+      </c>
+      <c r="AM16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>233.29</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1776,6 +2626,57 @@
       <c r="W17" t="n">
         <v>215.44</v>
       </c>
+      <c r="X17" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>61.03</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>40.68</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>23.01</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>106.42</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>222.54</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>161.08</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>330.5</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>280.31</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>32.66</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>163.98</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>40.48</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>215.44</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1853,6 +2754,57 @@
       <c r="W18" t="n">
         <v>195.39</v>
       </c>
+      <c r="X18" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>59.58</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>66.84999999999999</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>8.98</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>56.04</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>181.09</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>305.65</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>238.67</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>273.71</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>73.64</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>173.97</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>36.71</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>195.39</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1930,6 +2882,57 @@
       <c r="W19" t="n">
         <v>224.49</v>
       </c>
+      <c r="X19" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>62.7</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>46.94</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>48.49</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>240.24</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>180.74</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>254.97</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>94.3</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>6.58</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>170.02</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>44.96</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>224.49</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
@@ -2007,6 +3010,57 @@
       <c r="W20" t="n">
         <v>206.23</v>
       </c>
+      <c r="X20" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>48.53</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>32.82</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>22.83</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>39.73</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>14.47</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>213.67</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>179.55</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>162.3</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>171.49</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>36.18</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>177.1</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>53.21</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>206.23</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
@@ -2084,6 +3138,57 @@
       <c r="W21" t="n">
         <v>164.97</v>
       </c>
+      <c r="X21" t="n">
+        <v>4.56</v>
+      </c>
+      <c r="Y21" t="n">
+        <v>38.72</v>
+      </c>
+      <c r="Z21" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>28.63</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>72.83</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>160.31</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>108.94</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>200.77</v>
+      </c>
+      <c r="AI21" t="n">
+        <v>101.44</v>
+      </c>
+      <c r="AJ21" t="n">
+        <v>10.74</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>160.34</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>20.38</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>10.46</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>164.97</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
@@ -2161,6 +3266,57 @@
       <c r="W22" t="n">
         <v>189.34</v>
       </c>
+      <c r="X22" t="n">
+        <v>6.77</v>
+      </c>
+      <c r="Y22" t="n">
+        <v>70.45</v>
+      </c>
+      <c r="Z22" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>14.49</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>13.88</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>15.21</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="AE22" t="n">
+        <v>52.56</v>
+      </c>
+      <c r="AF22" t="n">
+        <v>197.29</v>
+      </c>
+      <c r="AG22" t="n">
+        <v>182.57</v>
+      </c>
+      <c r="AH22" t="n">
+        <v>190.8</v>
+      </c>
+      <c r="AI22" t="n">
+        <v>140.14</v>
+      </c>
+      <c r="AJ22" t="n">
+        <v>24.45</v>
+      </c>
+      <c r="AK22" t="n">
+        <v>169.58</v>
+      </c>
+      <c r="AL22" t="n">
+        <v>47.98</v>
+      </c>
+      <c r="AM22" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>189.34</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
@@ -2238,6 +3394,57 @@
       <c r="W23" t="n">
         <v>217.22</v>
       </c>
+      <c r="X23" t="n">
+        <v>4</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>80.66</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA23" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AB23" t="n">
+        <v>10.68</v>
+      </c>
+      <c r="AC23" t="n">
+        <v>18.62</v>
+      </c>
+      <c r="AD23" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="AE23" t="n">
+        <v>26.43</v>
+      </c>
+      <c r="AF23" t="n">
+        <v>210.39</v>
+      </c>
+      <c r="AG23" t="n">
+        <v>188.39</v>
+      </c>
+      <c r="AH23" t="n">
+        <v>221.73</v>
+      </c>
+      <c r="AI23" t="n">
+        <v>195.55</v>
+      </c>
+      <c r="AJ23" t="n">
+        <v>43.23</v>
+      </c>
+      <c r="AK23" t="n">
+        <v>173.09</v>
+      </c>
+      <c r="AL23" t="n">
+        <v>50.51</v>
+      </c>
+      <c r="AM23" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>217.22</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
@@ -2315,6 +3522,57 @@
       <c r="W24" t="n">
         <v>185.31</v>
       </c>
+      <c r="X24" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="Y24" t="n">
+        <v>33.2</v>
+      </c>
+      <c r="Z24" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA24" t="n">
+        <v>50.37</v>
+      </c>
+      <c r="AB24" t="n">
+        <v>2.73</v>
+      </c>
+      <c r="AC24" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD24" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="AE24" t="n">
+        <v>211.18</v>
+      </c>
+      <c r="AF24" t="n">
+        <v>252.96</v>
+      </c>
+      <c r="AG24" t="n">
+        <v>243.82</v>
+      </c>
+      <c r="AH24" t="n">
+        <v>174.21</v>
+      </c>
+      <c r="AI24" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AJ24" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="AK24" t="n">
+        <v>102.44</v>
+      </c>
+      <c r="AL24" t="n">
+        <v>39.09</v>
+      </c>
+      <c r="AM24" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>185.31</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
@@ -2392,6 +3650,57 @@
       <c r="W25" t="n">
         <v>232.97</v>
       </c>
+      <c r="X25" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="Y25" t="n">
+        <v>26.37</v>
+      </c>
+      <c r="Z25" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA25" t="n">
+        <v>12.94</v>
+      </c>
+      <c r="AB25" t="n">
+        <v>9.449999999999999</v>
+      </c>
+      <c r="AC25" t="n">
+        <v>42.64</v>
+      </c>
+      <c r="AD25" t="n">
+        <v>64.72</v>
+      </c>
+      <c r="AE25" t="n">
+        <v>34.36</v>
+      </c>
+      <c r="AF25" t="n">
+        <v>306.27</v>
+      </c>
+      <c r="AG25" t="n">
+        <v>268.3</v>
+      </c>
+      <c r="AH25" t="n">
+        <v>246.99</v>
+      </c>
+      <c r="AI25" t="n">
+        <v>279.3</v>
+      </c>
+      <c r="AJ25" t="n">
+        <v>42.8</v>
+      </c>
+      <c r="AK25" t="n">
+        <v>183.78</v>
+      </c>
+      <c r="AL25" t="n">
+        <v>60.34</v>
+      </c>
+      <c r="AM25" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>232.97</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
@@ -2469,6 +3778,57 @@
       <c r="W26" t="n">
         <v>265.65</v>
       </c>
+      <c r="X26" t="n">
+        <v>10.23</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>28.94</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>14.84</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>10.87</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>270.17</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>181.57</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>203.78</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>228.26</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>117.7</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>301.34</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>71.93000000000001</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>265.65</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
@@ -2546,6 +3906,57 @@
       <c r="W27" t="n">
         <v>243.81</v>
       </c>
+      <c r="X27" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>44.67</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>26.04</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>9.220000000000001</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>223.62</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>183.02</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>181.52</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>221.43</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>64.14</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>212.83</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>50.67</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>243.81</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
@@ -2623,6 +4034,57 @@
       <c r="W28" t="n">
         <v>248.28</v>
       </c>
+      <c r="X28" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>19.68</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>23.06</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>56.87</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>8.68</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>318.48</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>196.41</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>141.99</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>194.82</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>240.89</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>88.81</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>248.28</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
@@ -2700,6 +4162,57 @@
       <c r="W29" t="n">
         <v>219.69</v>
       </c>
+      <c r="X29" t="n">
+        <v>12.05</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>33.74</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>16.82</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>12.68</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>17.76</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>235.26</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>176.97</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>254.48</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>267.91</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>130.64</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>230.19</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>33.85</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>219.69</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
@@ -2777,6 +4290,57 @@
       <c r="W30" t="n">
         <v>224.37</v>
       </c>
+      <c r="X30" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>21.01</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>17.87</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>60.2</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>307.27</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>205.18</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>133.49</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>186.47</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>6.88</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>206.98</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>121.85</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>224.37</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
@@ -2854,6 +4418,57 @@
       <c r="W31" t="n">
         <v>230.64</v>
       </c>
+      <c r="X31" t="n">
+        <v>6.62</v>
+      </c>
+      <c r="Y31" t="n">
+        <v>30.91</v>
+      </c>
+      <c r="Z31" t="n">
+        <v>2025</v>
+      </c>
+      <c r="AA31" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="AB31" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="AC31" t="n">
+        <v>41.93</v>
+      </c>
+      <c r="AD31" t="n">
+        <v>56.56</v>
+      </c>
+      <c r="AE31" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="AF31" t="n">
+        <v>294.99</v>
+      </c>
+      <c r="AG31" t="n">
+        <v>191.3</v>
+      </c>
+      <c r="AH31" t="n">
+        <v>166.28</v>
+      </c>
+      <c r="AI31" t="n">
+        <v>232.7</v>
+      </c>
+      <c r="AJ31" t="n">
+        <v>90.34999999999999</v>
+      </c>
+      <c r="AK31" t="n">
+        <v>260.72</v>
+      </c>
+      <c r="AL31" t="n">
+        <v>57.32</v>
+      </c>
+      <c r="AM31" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>230.64</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
@@ -2931,6 +4546,57 @@
       <c r="W32" t="n">
         <v>207.7</v>
       </c>
+      <c r="X32" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="Y32" t="n">
+        <v>39.14</v>
+      </c>
+      <c r="Z32" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA32" t="n">
+        <v>25.7</v>
+      </c>
+      <c r="AB32" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="AC32" t="n">
+        <v>58.02</v>
+      </c>
+      <c r="AD32" t="n">
+        <v>22.6</v>
+      </c>
+      <c r="AE32" t="n">
+        <v>14.51</v>
+      </c>
+      <c r="AF32" t="n">
+        <v>244.68</v>
+      </c>
+      <c r="AG32" t="n">
+        <v>198.22</v>
+      </c>
+      <c r="AH32" t="n">
+        <v>132.72</v>
+      </c>
+      <c r="AI32" t="n">
+        <v>173.59</v>
+      </c>
+      <c r="AJ32" t="n">
+        <v>28.6</v>
+      </c>
+      <c r="AK32" t="n">
+        <v>241.58</v>
+      </c>
+      <c r="AL32" t="n">
+        <v>94.54000000000001</v>
+      </c>
+      <c r="AM32" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>207.7</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
@@ -3008,6 +4674,57 @@
       <c r="W33" t="n">
         <v>188.86</v>
       </c>
+      <c r="X33" t="n">
+        <v>4.73</v>
+      </c>
+      <c r="Y33" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="Z33" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA33" t="n">
+        <v>44.31</v>
+      </c>
+      <c r="AB33" t="n">
+        <v>40.05</v>
+      </c>
+      <c r="AC33" t="n">
+        <v>88.12</v>
+      </c>
+      <c r="AD33" t="n">
+        <v>66.79000000000001</v>
+      </c>
+      <c r="AE33" t="n">
+        <v>79.88</v>
+      </c>
+      <c r="AF33" t="n">
+        <v>273.65</v>
+      </c>
+      <c r="AG33" t="n">
+        <v>185.43</v>
+      </c>
+      <c r="AH33" t="n">
+        <v>138.5</v>
+      </c>
+      <c r="AI33" t="n">
+        <v>215.26</v>
+      </c>
+      <c r="AJ33" t="n">
+        <v>23.47</v>
+      </c>
+      <c r="AK33" t="n">
+        <v>256.7</v>
+      </c>
+      <c r="AL33" t="n">
+        <v>87.69</v>
+      </c>
+      <c r="AM33" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>188.86</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
@@ -3085,6 +4802,57 @@
       <c r="W34" t="n">
         <v>231.49</v>
       </c>
+      <c r="X34" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="Y34" t="n">
+        <v>28.99</v>
+      </c>
+      <c r="Z34" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA34" t="n">
+        <v>47.1</v>
+      </c>
+      <c r="AB34" t="n">
+        <v>55.01</v>
+      </c>
+      <c r="AC34" t="n">
+        <v>115.97</v>
+      </c>
+      <c r="AD34" t="n">
+        <v>73.79000000000001</v>
+      </c>
+      <c r="AE34" t="n">
+        <v>76.20999999999999</v>
+      </c>
+      <c r="AF34" t="n">
+        <v>232.28</v>
+      </c>
+      <c r="AG34" t="n">
+        <v>187.86</v>
+      </c>
+      <c r="AH34" t="n">
+        <v>134.3</v>
+      </c>
+      <c r="AI34" t="n">
+        <v>229.18</v>
+      </c>
+      <c r="AJ34" t="n">
+        <v>35.07</v>
+      </c>
+      <c r="AK34" t="n">
+        <v>270.03</v>
+      </c>
+      <c r="AL34" t="n">
+        <v>104.32</v>
+      </c>
+      <c r="AM34" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>231.49</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
@@ -3162,6 +4930,57 @@
       <c r="W35" t="n">
         <v>242.08</v>
       </c>
+      <c r="X35" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>18.74</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>2023</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>26.94</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>45.6</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>87.65000000000001</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>59.12</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>56.96</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>295.52</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>212.51</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>149.74</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>257.01</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>34.41</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>178.26</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>48.07</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>242.08</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
@@ -3239,6 +5058,57 @@
       <c r="W36" t="n">
         <v>165.5</v>
       </c>
+      <c r="X36" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="Y36" t="n">
+        <v>43.27</v>
+      </c>
+      <c r="Z36" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA36" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="AB36" t="n">
+        <v>18.22</v>
+      </c>
+      <c r="AC36" t="n">
+        <v>80.45</v>
+      </c>
+      <c r="AD36" t="n">
+        <v>28.53</v>
+      </c>
+      <c r="AE36" t="n">
+        <v>17.36</v>
+      </c>
+      <c r="AF36" t="n">
+        <v>120.95</v>
+      </c>
+      <c r="AG36" t="n">
+        <v>214.83</v>
+      </c>
+      <c r="AH36" t="n">
+        <v>161.12</v>
+      </c>
+      <c r="AI36" t="n">
+        <v>186.08</v>
+      </c>
+      <c r="AJ36" t="n">
+        <v>35.26</v>
+      </c>
+      <c r="AK36" t="n">
+        <v>198.59</v>
+      </c>
+      <c r="AL36" t="n">
+        <v>75.58</v>
+      </c>
+      <c r="AM36" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>165.5</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
@@ -3316,6 +5186,57 @@
       <c r="W37" t="n">
         <v>121.34</v>
       </c>
+      <c r="X37" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="Y37" t="n">
+        <v>40.99</v>
+      </c>
+      <c r="Z37" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA37" t="n">
+        <v>32.02</v>
+      </c>
+      <c r="AB37" t="n">
+        <v>34.57</v>
+      </c>
+      <c r="AC37" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="AD37" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="AE37" t="n">
+        <v>18.34</v>
+      </c>
+      <c r="AF37" t="n">
+        <v>129.17</v>
+      </c>
+      <c r="AG37" t="n">
+        <v>171.43</v>
+      </c>
+      <c r="AH37" t="n">
+        <v>139.86</v>
+      </c>
+      <c r="AI37" t="n">
+        <v>223.28</v>
+      </c>
+      <c r="AJ37" t="n">
+        <v>55.24</v>
+      </c>
+      <c r="AK37" t="n">
+        <v>223.64</v>
+      </c>
+      <c r="AL37" t="n">
+        <v>70.90000000000001</v>
+      </c>
+      <c r="AM37" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>121.34</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
@@ -3393,6 +5314,57 @@
       <c r="W38" t="n">
         <v>88.75</v>
       </c>
+      <c r="X38" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>59.57</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>11.96</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>18.96</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>53.46</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>42.89</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>21.29</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>164.91</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>161.01</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>93.56</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>188.21</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>6.93</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>235.81</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>78.84999999999999</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>88.75</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
@@ -3470,6 +5442,57 @@
       <c r="W39" t="n">
         <v>121.41</v>
       </c>
+      <c r="X39" t="n">
+        <v>7.04</v>
+      </c>
+      <c r="Y39" t="n">
+        <v>44.28</v>
+      </c>
+      <c r="Z39" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA39" t="n">
+        <v>19.02</v>
+      </c>
+      <c r="AB39" t="n">
+        <v>17.27</v>
+      </c>
+      <c r="AC39" t="n">
+        <v>66.81999999999999</v>
+      </c>
+      <c r="AD39" t="n">
+        <v>41.25</v>
+      </c>
+      <c r="AE39" t="n">
+        <v>5.53</v>
+      </c>
+      <c r="AF39" t="n">
+        <v>269.22</v>
+      </c>
+      <c r="AG39" t="n">
+        <v>213.03</v>
+      </c>
+      <c r="AH39" t="n">
+        <v>135.68</v>
+      </c>
+      <c r="AI39" t="n">
+        <v>206.48</v>
+      </c>
+      <c r="AJ39" t="n">
+        <v>48.05</v>
+      </c>
+      <c r="AK39" t="n">
+        <v>197.31</v>
+      </c>
+      <c r="AL39" t="n">
+        <v>76.33</v>
+      </c>
+      <c r="AM39" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>121.41</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
@@ -3547,6 +5570,57 @@
       <c r="W40" t="n">
         <v>144.37</v>
       </c>
+      <c r="X40" t="n">
+        <v>12.26</v>
+      </c>
+      <c r="Y40" t="n">
+        <v>47.34</v>
+      </c>
+      <c r="Z40" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA40" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="AB40" t="n">
+        <v>5.52</v>
+      </c>
+      <c r="AC40" t="n">
+        <v>59.75</v>
+      </c>
+      <c r="AD40" t="n">
+        <v>79.3</v>
+      </c>
+      <c r="AE40" t="n">
+        <v>21.5</v>
+      </c>
+      <c r="AF40" t="n">
+        <v>250.45</v>
+      </c>
+      <c r="AG40" t="n">
+        <v>224.73</v>
+      </c>
+      <c r="AH40" t="n">
+        <v>179.03</v>
+      </c>
+      <c r="AI40" t="n">
+        <v>257.66</v>
+      </c>
+      <c r="AJ40" t="n">
+        <v>60.33</v>
+      </c>
+      <c r="AK40" t="n">
+        <v>243.01</v>
+      </c>
+      <c r="AL40" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AM40" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>144.37</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
@@ -3624,6 +5698,57 @@
       <c r="W41" t="n">
         <v>125.49</v>
       </c>
+      <c r="X41" t="n">
+        <v>8.07</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>36.96</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>19</v>
+      </c>
+      <c r="AB41" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="AC41" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="AD41" t="n">
+        <v>57.31</v>
+      </c>
+      <c r="AE41" t="n">
+        <v>18.6</v>
+      </c>
+      <c r="AF41" t="n">
+        <v>305.76</v>
+      </c>
+      <c r="AG41" t="n">
+        <v>253.85</v>
+      </c>
+      <c r="AH41" t="n">
+        <v>210.6</v>
+      </c>
+      <c r="AI41" t="n">
+        <v>222.16</v>
+      </c>
+      <c r="AJ41" t="n">
+        <v>48.9</v>
+      </c>
+      <c r="AK41" t="n">
+        <v>232.26</v>
+      </c>
+      <c r="AL41" t="n">
+        <v>86.23</v>
+      </c>
+      <c r="AM41" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>125.49</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
@@ -3701,6 +5826,57 @@
       <c r="W42" t="n">
         <v>89.59999999999999</v>
       </c>
+      <c r="X42" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="Y42" t="n">
+        <v>34.53</v>
+      </c>
+      <c r="Z42" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA42" t="n">
+        <v>23.42</v>
+      </c>
+      <c r="AB42" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="AC42" t="n">
+        <v>50.42</v>
+      </c>
+      <c r="AD42" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="AE42" t="n">
+        <v>30.65</v>
+      </c>
+      <c r="AF42" t="n">
+        <v>188.01</v>
+      </c>
+      <c r="AG42" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="AH42" t="n">
+        <v>124.37</v>
+      </c>
+      <c r="AI42" t="n">
+        <v>211.57</v>
+      </c>
+      <c r="AJ42" t="n">
+        <v>20.97</v>
+      </c>
+      <c r="AK42" t="n">
+        <v>250.35</v>
+      </c>
+      <c r="AL42" t="n">
+        <v>68.68000000000001</v>
+      </c>
+      <c r="AM42" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>89.59999999999999</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
@@ -3778,6 +5954,57 @@
       <c r="W43" t="n">
         <v>197.3</v>
       </c>
+      <c r="X43" t="n">
+        <v>7.58</v>
+      </c>
+      <c r="Y43" t="n">
+        <v>48.93</v>
+      </c>
+      <c r="Z43" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA43" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="AB43" t="n">
+        <v>5.06</v>
+      </c>
+      <c r="AC43" t="n">
+        <v>60.1</v>
+      </c>
+      <c r="AD43" t="n">
+        <v>68.2</v>
+      </c>
+      <c r="AE43" t="n">
+        <v>39.42</v>
+      </c>
+      <c r="AF43" t="n">
+        <v>235.77</v>
+      </c>
+      <c r="AG43" t="n">
+        <v>202.57</v>
+      </c>
+      <c r="AH43" t="n">
+        <v>256.33</v>
+      </c>
+      <c r="AI43" t="n">
+        <v>210.47</v>
+      </c>
+      <c r="AJ43" t="n">
+        <v>22.2</v>
+      </c>
+      <c r="AK43" t="n">
+        <v>248.17</v>
+      </c>
+      <c r="AL43" t="n">
+        <v>122.36</v>
+      </c>
+      <c r="AM43" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>197.3</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
@@ -3855,6 +6082,57 @@
       <c r="W44" t="n">
         <v>270.92</v>
       </c>
+      <c r="X44" t="n">
+        <v>5.28</v>
+      </c>
+      <c r="Y44" t="n">
+        <v>25.02</v>
+      </c>
+      <c r="Z44" t="n">
+        <v>2022</v>
+      </c>
+      <c r="AA44" t="n">
+        <v>17.17</v>
+      </c>
+      <c r="AB44" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AC44" t="n">
+        <v>60.06</v>
+      </c>
+      <c r="AD44" t="n">
+        <v>30.07</v>
+      </c>
+      <c r="AE44" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AF44" t="n">
+        <v>261.41</v>
+      </c>
+      <c r="AG44" t="n">
+        <v>219.77</v>
+      </c>
+      <c r="AH44" t="n">
+        <v>239.34</v>
+      </c>
+      <c r="AI44" t="n">
+        <v>242.33</v>
+      </c>
+      <c r="AJ44" t="n">
+        <v>22.74</v>
+      </c>
+      <c r="AK44" t="n">
+        <v>256.63</v>
+      </c>
+      <c r="AL44" t="n">
+        <v>132.76</v>
+      </c>
+      <c r="AM44" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>270.92</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
@@ -3930,6 +6208,57 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
+        <v>229.52</v>
+      </c>
+      <c r="X45" t="n">
+        <v>8.91</v>
+      </c>
+      <c r="Y45" t="n">
+        <v>40.41</v>
+      </c>
+      <c r="Z45" t="n">
+        <v>2020</v>
+      </c>
+      <c r="AA45" t="n">
+        <v>23.28</v>
+      </c>
+      <c r="AB45" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="AC45" t="n">
+        <v>73.18000000000001</v>
+      </c>
+      <c r="AD45" t="n">
+        <v>40.29</v>
+      </c>
+      <c r="AE45" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AF45" t="n">
+        <v>233.43</v>
+      </c>
+      <c r="AG45" t="n">
+        <v>221.11</v>
+      </c>
+      <c r="AH45" t="n">
+        <v>242.92</v>
+      </c>
+      <c r="AI45" t="n">
+        <v>203.42</v>
+      </c>
+      <c r="AJ45" t="n">
+        <v>14.63</v>
+      </c>
+      <c r="AK45" t="n">
+        <v>219.46</v>
+      </c>
+      <c r="AL45" t="n">
+        <v>88.63</v>
+      </c>
+      <c r="AM45" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN45" t="n">
         <v>229.52</v>
       </c>
     </row>
